--- a/verification/cases/scratch/conditional_formatting/init.xlsx
+++ b/verification/cases/scratch/conditional_formatting/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10812"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Troldal/Development/bin2c/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC33A6FB-1603-2641-A40F-B7C7F2B0E698}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA5AE2B2-8BC0-468E-A676-E91D1518025E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1560" windowWidth="28040" windowHeight="17440" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,18 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <si>
-    <t/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts>
-	</numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -93,9 +83,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -133,7 +123,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -239,7 +229,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -381,7 +371,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -390,7 +380,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
